--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:15</t>
+    <t xml:space="preserve">2026-09-09 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:10</t>
+    <t xml:space="preserve">2026-09-17 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:06</t>
+    <t xml:space="preserve">2026-09-23 12:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:35</t>
+    <t xml:space="preserve">2026-10-02 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Pemuco</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:04</t>
+    <t xml:space="preserve">2026-10-04 09:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:00</t>
+    <t xml:space="preserve">2026-10-05 10:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
